--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -3643,6 +3643,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -3660,20 +3670,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
@@ -3693,6 +3692,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -29498,8 +29498,8 @@
       <c r="D15" t="s">
         <v>352</v>
       </c>
-      <c r="E15" s="41">
-        <v>0.02</v>
+      <c r="E15" s="34">
+        <v>2</v>
       </c>
       <c r="G15" t="s">
         <v>353</v>

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -589,7 +589,7 @@
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2708,13 +2708,13 @@
     <t>Trd_bus_elc_134</t>
   </si>
   <si>
+    <t>Trd_car_elc_200</t>
+  </si>
+  <si>
+    <t>Trd_bus_elc_149</t>
+  </si>
+  <si>
     <t>~UC_T: UC_RHSRT~UP</t>
-  </si>
-  <si>
-    <t>Trd_car_elc_200</t>
-  </si>
-  <si>
-    <t>Trd_bus_elc_149</t>
   </si>
   <si>
     <t>~UC_T: UC_RHSRT~FX</t>
@@ -3559,11 +3559,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -3571,11 +3566,17 @@
     </font>
     <font>
       <b/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -3587,12 +3588,11 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
@@ -18285,9 +18285,6 @@
     <row r="4" ht="29" spans="1:34">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="7" t="s">
-        <v>658</v>
-      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -18311,7 +18308,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AA4" s="14">
         <v>36</v>
@@ -18321,7 +18318,7 @@
         <v>-36</v>
       </c>
       <c r="AF4" s="14" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG4" s="14">
         <v>149</v>
@@ -18334,6 +18331,9 @@
     <row r="5" ht="29" spans="1:34">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>660</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -18671,7 +18671,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -18688,7 +18688,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U10" s="15"/>
       <c r="V10" s="15"/>
@@ -19675,7 +19675,7 @@
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="16" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AA28" s="14">
         <v>149</v>
@@ -19925,7 +19925,7 @@
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U34" s="15"/>
       <c r="V34" s="15"/>
@@ -21661,7 +21661,7 @@
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -21805,7 +21805,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J10" s="5"/>
       <c r="L10" s="5"/>

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -589,7 +589,7 @@
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="C5" authorId="0">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2708,13 +2708,13 @@
     <t>Trd_bus_elc_134</t>
   </si>
   <si>
+    <t>~UC_T: UC_RHSRT~UP</t>
+  </si>
+  <si>
     <t>Trd_car_elc_200</t>
   </si>
   <si>
     <t>Trd_bus_elc_149</t>
-  </si>
-  <si>
-    <t>~UC_T: UC_RHSRT~UP</t>
   </si>
   <si>
     <t>~UC_T: UC_RHSRT~FX</t>
@@ -3561,8 +3561,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -3578,13 +3588,8 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -3596,11 +3601,6 @@
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -18285,6 +18285,9 @@
     <row r="4" ht="29" spans="1:34">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
+      <c r="C4" s="7" t="s">
+        <v>658</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -18308,7 +18311,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="16" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA4" s="14">
         <v>36</v>
@@ -18318,7 +18321,7 @@
         <v>-36</v>
       </c>
       <c r="AF4" s="14" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG4" s="14">
         <v>149</v>
@@ -18331,9 +18334,6 @@
     <row r="5" ht="29" spans="1:34">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
-        <v>660</v>
-      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -18671,7 +18671,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -18688,7 +18688,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="U10" s="15"/>
       <c r="V10" s="15"/>
@@ -19675,7 +19675,7 @@
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="16" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA28" s="14">
         <v>149</v>
@@ -19925,7 +19925,7 @@
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="U34" s="15"/>
       <c r="V34" s="15"/>
@@ -21661,7 +21661,7 @@
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -21805,7 +21805,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J10" s="5"/>
       <c r="L10" s="5"/>

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -589,7 +589,7 @@
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2708,13 +2708,13 @@
     <t>Trd_bus_elc_134</t>
   </si>
   <si>
+    <t>Trd_car_elc_200</t>
+  </si>
+  <si>
+    <t>Trd_bus_elc_149</t>
+  </si>
+  <si>
     <t>~UC_T: UC_RHSRT~UP</t>
-  </si>
-  <si>
-    <t>Trd_car_elc_200</t>
-  </si>
-  <si>
-    <t>Trd_bus_elc_149</t>
   </si>
   <si>
     <t>~UC_T: UC_RHSRT~FX</t>
@@ -3566,12 +3566,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3581,8 +3576,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3603,12 +3598,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -18285,9 +18285,6 @@
     <row r="4" ht="29" spans="1:34">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="7" t="s">
-        <v>658</v>
-      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -18311,7 +18308,7 @@
       <c r="X4" s="15"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AA4" s="14">
         <v>36</v>
@@ -18321,7 +18318,7 @@
         <v>-36</v>
       </c>
       <c r="AF4" s="14" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG4" s="14">
         <v>149</v>
@@ -18334,6 +18331,9 @@
     <row r="5" ht="29" spans="1:34">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>660</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -18405,7 +18405,9 @@
       <c r="I6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J6" s="6"/>
+      <c r="J6" s="6">
+        <v>2120</v>
+      </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="7" t="s">
@@ -18485,7 +18487,9 @@
       <c r="I7" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="J7" s="6"/>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="7" t="s">
@@ -18671,7 +18675,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -18688,7 +18692,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U10" s="15"/>
       <c r="V10" s="15"/>
@@ -19675,7 +19679,7 @@
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="16" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AA28" s="14">
         <v>149</v>
@@ -19925,7 +19929,7 @@
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U34" s="15"/>
       <c r="V34" s="15"/>
@@ -21661,7 +21665,7 @@
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -21805,7 +21809,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J10" s="5"/>
       <c r="L10" s="5"/>

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -3559,9 +3559,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3570,8 +3587,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
@@ -3589,26 +3605,10 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -18405,9 +18405,7 @@
       <c r="I6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J6" s="6">
-        <v>2120</v>
-      </c>
+      <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="7" t="s">
@@ -18479,7 +18477,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>667</v>
@@ -18487,9 +18485,7 @@
       <c r="I7" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
+      <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="7" t="s">

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -23471,14 +23471,18 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>1</v>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>*~UC_SETS: R_E: AllRegions (disabled: sheet marked REMOVED)</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="41"/>
-      <c r="C3" s="43" t="s">
-        <v>661</v>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>*~UC_T: UC_RHSRT~UP</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -22177,7 +22177,7 @@
       </c>
       <c r="O48" s="49"/>
       <c r="P48" s="48" t="n">
-        <v>-2</v>
+        <v>-1.0</v>
       </c>
       <c r="Q48" s="49"/>
       <c r="R48" s="49"/>
@@ -22203,7 +22203,7 @@
       </c>
       <c r="O49" s="49"/>
       <c r="P49" s="48" t="n">
-        <v>-2.18</v>
+        <v>-1.09</v>
       </c>
       <c r="Q49" s="49"/>
       <c r="R49" s="49"/>
@@ -22229,7 +22229,7 @@
       </c>
       <c r="O50" s="49"/>
       <c r="P50" s="48" t="n">
-        <v>-2.34</v>
+        <v>-1.17</v>
       </c>
       <c r="Q50" s="49"/>
       <c r="R50" s="49"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="O51" s="49"/>
       <c r="P51" s="48" t="n">
-        <v>-2.52</v>
+        <v>-1.26</v>
       </c>
       <c r="Q51" s="49"/>
       <c r="R51" s="49"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="O52" s="49"/>
       <c r="P52" s="48" t="n">
-        <v>-2.68</v>
+        <v>-1.34</v>
       </c>
       <c r="Q52" s="49"/>
       <c r="R52" s="49"/>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="O53" s="49"/>
       <c r="P53" s="48" t="n">
-        <v>-2.86</v>
+        <v>-1.43</v>
       </c>
       <c r="Q53" s="49"/>
       <c r="R53" s="49"/>
@@ -22333,7 +22333,7 @@
       </c>
       <c r="O54" s="49"/>
       <c r="P54" s="48" t="n">
-        <v>-3.02</v>
+        <v>-1.51</v>
       </c>
       <c r="Q54" s="49"/>
       <c r="R54" s="49"/>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="O55" s="49"/>
       <c r="P55" s="48" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="Q55" s="49"/>
       <c r="R55" s="49"/>
@@ -22385,7 +22385,7 @@
       </c>
       <c r="O56" s="49"/>
       <c r="P56" s="48" t="n">
-        <v>-3.6</v>
+        <v>-2.52</v>
       </c>
       <c r="Q56" s="49"/>
       <c r="R56" s="49"/>
@@ -22411,7 +22411,7 @@
       </c>
       <c r="O57" s="49"/>
       <c r="P57" s="48" t="n">
-        <v>-3.93</v>
+        <v>-2.751</v>
       </c>
       <c r="Q57" s="49"/>
       <c r="R57" s="49"/>
@@ -22437,7 +22437,7 @@
       </c>
       <c r="O58" s="49"/>
       <c r="P58" s="48" t="n">
-        <v>-4.29</v>
+        <v>-3.003</v>
       </c>
       <c r="Q58" s="49"/>
       <c r="R58" s="49"/>
@@ -22463,7 +22463,7 @@
       </c>
       <c r="O59" s="49"/>
       <c r="P59" s="48" t="n">
-        <v>-4.62</v>
+        <v>-3.234</v>
       </c>
       <c r="Q59" s="49"/>
       <c r="R59" s="49"/>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="O60" s="49"/>
       <c r="P60" s="48" t="n">
-        <v>-4.98</v>
+        <v>-3.486</v>
       </c>
       <c r="Q60" s="49"/>
       <c r="R60" s="49"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="O61" s="49"/>
       <c r="P61" s="48" t="n">
-        <v>-5.31</v>
+        <v>-3.717</v>
       </c>
       <c r="Q61" s="49"/>
       <c r="R61" s="49"/>
@@ -22541,7 +22541,7 @@
       </c>
       <c r="O62" s="49"/>
       <c r="P62" s="48" t="n">
-        <v>-5.67</v>
+        <v>-3.969</v>
       </c>
       <c r="Q62" s="49"/>
       <c r="R62" s="49"/>
@@ -22567,7 +22567,7 @@
       </c>
       <c r="O63" s="49"/>
       <c r="P63" s="48" t="n">
-        <v>-6</v>
+        <v>-4.2</v>
       </c>
       <c r="Q63" s="49"/>
       <c r="R63" s="49"/>
